--- a/artfynd/A 51663-2022 artfynd.xlsx
+++ b/artfynd/A 51663-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51663-2022 artfynd.xlsx
+++ b/artfynd/A 51663-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111815508</v>
+        <v>111815517</v>
       </c>
       <c r="B2" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>rismon önö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458162</v>
+        <v>458251</v>
       </c>
       <c r="R2" t="n">
-        <v>7054329</v>
+        <v>7054376</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111815507</v>
+        <v>111815518</v>
       </c>
       <c r="B3" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>rismon önö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458152</v>
+        <v>458251</v>
       </c>
       <c r="R3" t="n">
-        <v>7054482</v>
+        <v>7054619</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111815516</v>
+        <v>111815519</v>
       </c>
       <c r="B4" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458290</v>
+        <v>458216</v>
       </c>
       <c r="R4" t="n">
-        <v>7054475</v>
+        <v>7054621</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111815510</v>
+        <v>111815507</v>
       </c>
       <c r="B5" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458204</v>
+        <v>458152</v>
       </c>
       <c r="R5" t="n">
-        <v>7054385</v>
+        <v>7054482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1045,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,15 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111815518</v>
+        <v>111815508</v>
       </c>
       <c r="B6" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,34 +1083,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>rismon önö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458251</v>
+        <v>458163</v>
       </c>
       <c r="R6" t="n">
-        <v>7054618</v>
+        <v>7054329</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,6 +1147,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,15 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111815517</v>
+        <v>111815509</v>
       </c>
       <c r="B7" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,34 +1189,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>rismon önö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458251</v>
+        <v>458176</v>
       </c>
       <c r="R7" t="n">
-        <v>7054375</v>
+        <v>7054363</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,6 +1253,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,15 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111815509</v>
+        <v>111815510</v>
       </c>
       <c r="B8" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458176</v>
+        <v>458204</v>
       </c>
       <c r="R8" t="n">
-        <v>7054363</v>
+        <v>7054385</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1363,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,15 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111815512</v>
+        <v>111815511</v>
       </c>
       <c r="B9" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458155</v>
+        <v>458305</v>
       </c>
       <c r="R9" t="n">
-        <v>7054646</v>
+        <v>7054609</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,15 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111815515</v>
+        <v>111815512</v>
       </c>
       <c r="B10" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,34 +1507,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>rismon önö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458162</v>
+        <v>458155</v>
       </c>
       <c r="R10" t="n">
-        <v>7054459</v>
+        <v>7054646</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,6 +1571,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,12 +1605,7 @@
         <v>111815513</v>
       </c>
       <c r="B11" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,210 +1706,6 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>111815519</v>
-      </c>
-      <c r="B12" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>rismon önö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>458216</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7054621</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>111815514</v>
-      </c>
-      <c r="B13" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>rismon önö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>458154</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7054482</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51663-2022 artfynd.xlsx
+++ b/artfynd/A 51663-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111815517</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111815518</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111815519</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111815507</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111815508</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111815509</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111815510</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111815511</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111815512</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1705,8 +1755,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111815513</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>